--- a/data/demo/AEK-Sales-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/AEK-Sales-2026-07-20~2026-07-20.xlsx
@@ -23,10 +23,10 @@
     <t>AEK-CYBER Barra de sonido para TV, dos altavoces de 2 pulgadas con imán de 45 + dos membranas para graves, sonido claro ≥75dB, Bluetooth inalámbrico y conexiones coaxial/AUX, diseño compacto de 81.2cm, sistema de sonido envolvente para Smart TV, adecuado para cine en casa/PC/juegos/fiestas</t>
   </si>
   <si>
-    <t>MX$675.00</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>MX$1,125.00</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>1.00</t>
